--- a/data/GPS/Metricas_GPS11.xlsx
+++ b/data/GPS/Metricas_GPS11.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30506"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C94BACC-4FD6-4281-A507-BC98EAA4D6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>eJy9lltv2jAUx7+KladNQhDCytJpmsSG+rKW0Va97aLK2A5x8SWK7dKC+O6zDe1CBqxkap6Sc3J8zu9/fMs8wFATFXwA80BL/3AO+xJEYdQND8N20ADBPWTOxVysDhbWk+SSvzTcxWf3GiVjV+jHfGXcUuyiuDEYzmg3nrqhSLJVkH1bRczElLpvGdSps31Ja+vHjBRtAbm3jwhKoXMYQbVzOOJiQhZarfY7VbdjT59Apoh15AQb5HNoqX0JOMYkWQ5rdw8OO9ZHhOHW4zF/FbAyqZokQ0UyO7zIwakocvZNDhGVoox3BE8vi3p9fCFrxuAjyYuZBpKPcrJL8vez6EuwDku1q70z79BGoVXUtsyYmruNzRzlRqXkuU3/3VtM1Y7eTvhaa6nSUCAKgS1mV2OJ+Wt6Fa8x69y8BvJMkOa7iuCfQDsGE95Ky/DHXZPWBd+tCG/po4NGBDYK+MYvTuoS8L6iANf/KG7EmxWcSvhQ3xQgoXcoWDsHfpowHEFwnuVUaAXefPwzC2//Wkfic68OERAhpyOqoKOHCCPLQ9IClfjbZ9e1bGJMKvP3iYK7JFwM1M1+ZydfLrwKc9B8Grrlbmqplipq6KEmOIEPlMMyNRoSvCf18uKrRE3FPtR9shU7SzqdWpqtMvyPZrv9uHbRXnroMnE/uhm8+tVK71STSfzClT30/wjgWEIcLFwaxCgRellKGMa883kfkCm4kvlkJOUkWPwGtu4QZA==</t>
   </si>
@@ -126,9 +135,6 @@
   </si>
   <si>
     <t xml:space="preserve">Juan_Manuel_Ruiz </t>
-  </si>
-  <si>
-    <t>Denfensa Lateral</t>
   </si>
   <si>
     <t xml:space="preserve">Noah_Ojo_Barranco </t>
@@ -140,25 +146,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -169,38 +176,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -208,7 +220,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -398,26 +410,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="133.25"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="133.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -426,21 +441,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -487,12 +503,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="2">
-        <v>82.667</v>
+        <v>82.667000000000002</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>18</v>
@@ -507,39 +523,39 @@
         <v>0.247</v>
       </c>
       <c r="G2" s="2">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K2" s="2">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2">
-        <v>4.543</v>
+        <v>4.5430000000000001</v>
       </c>
       <c r="M2" s="2">
-        <v>-4.379</v>
+        <v>-4.3789999999999996</v>
       </c>
       <c r="N2" s="2">
-        <v>28.364</v>
+        <v>28.364000000000001</v>
       </c>
       <c r="O2" s="2">
         <v>1017.616</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B3" s="2">
-        <v>78.967</v>
+        <v>78.966999999999999</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -548,45 +564,45 @@
         <v>21</v>
       </c>
       <c r="E3" s="2">
-        <v>3.882</v>
+        <v>3.8820000000000001</v>
       </c>
       <c r="F3" s="2">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="G3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="K3" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="L3" s="2">
-        <v>4.396</v>
+        <v>4.3959999999999999</v>
       </c>
       <c r="M3" s="2">
-        <v>-6.563</v>
+        <v>-6.5629999999999997</v>
       </c>
       <c r="N3" s="2">
-        <v>24.858</v>
+        <v>24.858000000000001</v>
       </c>
       <c r="O3" s="2">
-        <v>791.126</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>791.12599999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B4" s="2">
-        <v>78.633</v>
+        <v>78.632999999999996</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -595,45 +611,45 @@
         <v>23</v>
       </c>
       <c r="E4" s="2">
-        <v>4.401</v>
+        <v>4.4009999999999998</v>
       </c>
       <c r="F4" s="2">
-        <v>0.077</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="K4" s="2">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="L4" s="2">
-        <v>4.933</v>
+        <v>4.9329999999999998</v>
       </c>
       <c r="M4" s="2">
-        <v>-4.928</v>
+        <v>-4.9279999999999999</v>
       </c>
       <c r="N4" s="2">
         <v>23.31</v>
       </c>
       <c r="O4" s="2">
-        <v>681.885</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>681.88499999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B5" s="2">
-        <v>78.833</v>
+        <v>78.832999999999998</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>24</v>
@@ -648,39 +664,39 @@
         <v>0.115</v>
       </c>
       <c r="G5" s="2">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="H5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="K5" s="2">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2">
-        <v>4.171</v>
+        <v>4.1710000000000003</v>
       </c>
       <c r="M5" s="2">
-        <v>-4.911</v>
+        <v>-4.9109999999999996</v>
       </c>
       <c r="N5" s="2">
-        <v>27.144</v>
+        <v>27.143999999999998</v>
       </c>
       <c r="O5" s="2">
-        <v>709.908</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>709.90800000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B6" s="2">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>25</v>
@@ -689,45 +705,45 @@
         <v>23</v>
       </c>
       <c r="E6" s="2">
-        <v>4.063</v>
+        <v>4.0629999999999997</v>
       </c>
       <c r="F6" s="2">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="H6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="K6" s="2">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="L6" s="2">
-        <v>4.691</v>
+        <v>4.6909999999999998</v>
       </c>
       <c r="M6" s="2">
-        <v>-5.555</v>
+        <v>-5.5549999999999997</v>
       </c>
       <c r="N6" s="2">
-        <v>28.487</v>
+        <v>28.486999999999998</v>
       </c>
       <c r="O6" s="2">
-        <v>626.126</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>626.12599999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B7" s="2">
-        <v>78.867</v>
+        <v>78.867000000000004</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>26</v>
@@ -736,45 +752,45 @@
         <v>21</v>
       </c>
       <c r="E7" s="2">
-        <v>4.082</v>
+        <v>4.0819999999999999</v>
       </c>
       <c r="F7" s="2">
-        <v>0.076</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="G7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="K7" s="2">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="L7" s="2">
         <v>4.72</v>
       </c>
       <c r="M7" s="2">
-        <v>-5.449</v>
+        <v>-5.4489999999999998</v>
       </c>
       <c r="N7" s="2">
         <v>24.523</v>
       </c>
       <c r="O7" s="2">
-        <v>867.588</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>867.58799999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B8" s="2">
-        <v>81.383</v>
+        <v>81.382999999999996</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>27</v>
@@ -783,31 +799,31 @@
         <v>28</v>
       </c>
       <c r="E8" s="2">
-        <v>4.502</v>
+        <v>4.5019999999999998</v>
       </c>
       <c r="F8" s="2">
-        <v>0.268</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="G8" s="2">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J8" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="K8" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="L8" s="2">
-        <v>4.486</v>
+        <v>4.4859999999999998</v>
       </c>
       <c r="M8" s="2">
-        <v>-5.637</v>
+        <v>-5.6369999999999996</v>
       </c>
       <c r="N8" s="2">
         <v>27.997</v>
@@ -816,9 +832,9 @@
         <v>1062.146</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B9" s="2">
         <v>79.95</v>
@@ -830,45 +846,45 @@
         <v>23</v>
       </c>
       <c r="E9" s="2">
-        <v>4.376</v>
+        <v>4.3760000000000003</v>
       </c>
       <c r="F9" s="2">
-        <v>0.171</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>0.013</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="H9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K9" s="2">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="L9" s="2">
-        <v>4.717</v>
+        <v>4.7169999999999996</v>
       </c>
       <c r="M9" s="2">
-        <v>-6.087</v>
+        <v>-6.0869999999999997</v>
       </c>
       <c r="N9" s="2">
         <v>26.564</v>
       </c>
       <c r="O9" s="2">
-        <v>1026.801</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1026.8009999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B10" s="2">
-        <v>81.817</v>
+        <v>81.816999999999993</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>30</v>
@@ -877,45 +893,45 @@
         <v>28</v>
       </c>
       <c r="E10" s="2">
-        <v>5.146</v>
+        <v>5.1459999999999999</v>
       </c>
       <c r="F10" s="2">
-        <v>0.281</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="G10" s="2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="H10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="K10" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="L10" s="2">
-        <v>4.613</v>
+        <v>4.6130000000000004</v>
       </c>
       <c r="M10" s="2">
-        <v>-6.425</v>
+        <v>-6.4249999999999998</v>
       </c>
       <c r="N10" s="2">
-        <v>27.248</v>
+        <v>27.248000000000001</v>
       </c>
       <c r="O10" s="2">
         <v>1138.403</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B11" s="2">
-        <v>81.533</v>
+        <v>81.533000000000001</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -924,45 +940,45 @@
         <v>32</v>
       </c>
       <c r="E11" s="2">
-        <v>4.081</v>
+        <v>4.0810000000000004</v>
       </c>
       <c r="F11" s="2">
         <v>0.159</v>
       </c>
       <c r="G11" s="2">
-        <v>0.007</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="K11" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="L11" s="2">
-        <v>4.964</v>
+        <v>4.9640000000000004</v>
       </c>
       <c r="M11" s="2">
-        <v>-5.439</v>
+        <v>-5.4390000000000001</v>
       </c>
       <c r="N11" s="2">
-        <v>27.047</v>
+        <v>27.047000000000001</v>
       </c>
       <c r="O11" s="2">
-        <v>1141.757</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>1141.7570000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B12" s="2">
-        <v>78.1</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
@@ -971,45 +987,45 @@
         <v>32</v>
       </c>
       <c r="E12" s="2">
-        <v>3.656</v>
+        <v>3.6560000000000001</v>
       </c>
       <c r="F12" s="2">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="G12" s="2">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H12" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="K12" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="L12" s="2">
         <v>4.351</v>
       </c>
       <c r="M12" s="2">
-        <v>-5.318</v>
+        <v>-5.3179999999999996</v>
       </c>
       <c r="N12" s="2">
         <v>27.05</v>
       </c>
       <c r="O12" s="2">
-        <v>516.593</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>516.59299999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B13" s="2">
-        <v>81.733</v>
+        <v>81.733000000000004</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -1018,45 +1034,45 @@
         <v>28</v>
       </c>
       <c r="E13" s="2">
-        <v>4.503</v>
+        <v>4.5030000000000001</v>
       </c>
       <c r="F13" s="2">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="G13" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="K13" s="2">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="L13" s="2">
         <v>4.84</v>
       </c>
       <c r="M13" s="2">
-        <v>-5.445</v>
+        <v>-5.4450000000000003</v>
       </c>
       <c r="N13" s="2">
-        <v>25.114</v>
+        <v>25.114000000000001</v>
       </c>
       <c r="O13" s="2">
-        <v>1184.618</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>1184.6179999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B14" s="2">
-        <v>80.933</v>
+        <v>80.933000000000007</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>35</v>
@@ -1065,45 +1081,45 @@
         <v>19</v>
       </c>
       <c r="E14" s="2">
-        <v>3.708</v>
+        <v>3.7080000000000002</v>
       </c>
       <c r="F14" s="2">
         <v>0.129</v>
       </c>
       <c r="G14" s="2">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H14" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="L14" s="2">
-        <v>4.844</v>
+        <v>4.8440000000000003</v>
       </c>
       <c r="M14" s="2">
         <v>-4.32</v>
       </c>
       <c r="N14" s="2">
-        <v>26.874</v>
+        <v>26.873999999999999</v>
       </c>
       <c r="O14" s="2">
-        <v>721.337</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>721.33699999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B15" s="2">
-        <v>79.133</v>
+        <v>79.132999999999996</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>36</v>
@@ -1112,134 +1128,134 @@
         <v>32</v>
       </c>
       <c r="E15" s="2">
-        <v>4.677</v>
+        <v>4.6769999999999996</v>
       </c>
       <c r="F15" s="2">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="G15" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="K15" s="2">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="L15" s="2">
-        <v>5.073</v>
+        <v>5.0730000000000004</v>
       </c>
       <c r="M15" s="2">
-        <v>-5.279</v>
+        <v>-5.2789999999999999</v>
       </c>
       <c r="N15" s="2">
-        <v>24.761</v>
+        <v>24.760999999999999</v>
       </c>
       <c r="O15" s="2">
-        <v>38.981</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>38.981000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B16" s="2">
-        <v>77.983</v>
+        <v>77.983000000000004</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2">
-        <v>4.095</v>
+        <v>4.0949999999999998</v>
       </c>
       <c r="F16" s="2">
         <v>0.12</v>
       </c>
       <c r="G16" s="2">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="H16" s="2">
-        <v>0.007</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I16" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K16" s="2">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="L16" s="2">
-        <v>5.814</v>
+        <v>5.8140000000000001</v>
       </c>
       <c r="M16" s="2">
-        <v>-6.081</v>
+        <v>-6.0810000000000004</v>
       </c>
       <c r="N16" s="2">
-        <v>30.524</v>
+        <v>30.524000000000001</v>
       </c>
       <c r="O16" s="2">
-        <v>907.859</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>907.85900000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="B17" s="2">
-        <v>81.283</v>
+        <v>81.283000000000001</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E17" s="2">
-        <v>4.115</v>
+        <v>4.1150000000000002</v>
       </c>
       <c r="F17" s="2">
         <v>0.13</v>
       </c>
       <c r="G17" s="2">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="H17" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="K17" s="2">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="L17" s="2">
-        <v>4.818</v>
+        <v>4.8179999999999996</v>
       </c>
       <c r="M17" s="2">
-        <v>-6.251</v>
+        <v>-6.2510000000000003</v>
       </c>
       <c r="N17" s="2">
         <v>26.503</v>
       </c>
       <c r="O17" s="2">
-        <v>908.843</v>
+        <v>908.84299999999996</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>